--- a/engine/egch_study/EGCH_Valuation_Model_10092026.xlsx
+++ b/engine/egch_study/EGCH_Valuation_Model_10092026.xlsx
@@ -123,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -162,6 +162,7 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1167,23 +1168,23 @@
           <t>Capital expenditure</t>
         </is>
       </c>
-      <c r="B30" s="24">
+      <c r="B30" s="25">
         <f>-'DCF'!B12</f>
         <v/>
       </c>
-      <c r="C30" s="24">
+      <c r="C30" s="25">
         <f>-'DCF'!C12</f>
         <v/>
       </c>
-      <c r="D30" s="24">
+      <c r="D30" s="25">
         <f>-'DCF'!D12</f>
         <v/>
       </c>
-      <c r="E30" s="24">
+      <c r="E30" s="25">
         <f>-'DCF'!E12</f>
         <v/>
       </c>
-      <c r="F30" s="24">
+      <c r="F30" s="25">
         <f>-'DCF'!F12</f>
         <v/>
       </c>
@@ -1194,23 +1195,23 @@
           <t>Depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B31" s="24">
+      <c r="B31" s="25">
         <f>'Segments'!B25</f>
         <v/>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="25">
         <f>'Segments'!C25</f>
         <v/>
       </c>
-      <c r="D31" s="24">
+      <c r="D31" s="25">
         <f>'Segments'!D25</f>
         <v/>
       </c>
-      <c r="E31" s="24">
+      <c r="E31" s="25">
         <f>'Segments'!E25</f>
         <v/>
       </c>
-      <c r="F31" s="24">
+      <c r="F31" s="25">
         <f>'Segments'!F25</f>
         <v/>
       </c>
@@ -1318,23 +1319,23 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="25">
         <f>'Segments'!B18</f>
         <v/>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <f>'Segments'!C18</f>
         <v/>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <f>'Segments'!D18</f>
         <v/>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <f>'Segments'!E18</f>
         <v/>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <f>'Segments'!F18</f>
         <v/>
       </c>
@@ -1345,23 +1346,23 @@
           <t>Cost of sales</t>
         </is>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="25">
         <f>'Segments'!B26</f>
         <v/>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <f>'Segments'!C26</f>
         <v/>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <f>'Segments'!D26</f>
         <v/>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <f>'Segments'!E26</f>
         <v/>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <f>'Segments'!F26</f>
         <v/>
       </c>
@@ -1373,23 +1374,23 @@
         </is>
       </c>
       <c r="B7" s="14">
-        <f>B5*'Assumptions'!C144/365</f>
+        <f>B5*'Assumptions'!C149/365</f>
         <v/>
       </c>
       <c r="C7" s="14">
-        <f>C5*'Assumptions'!C144/365</f>
+        <f>C5*'Assumptions'!C149/365</f>
         <v/>
       </c>
       <c r="D7" s="14">
-        <f>D5*'Assumptions'!C144/365</f>
+        <f>D5*'Assumptions'!C149/365</f>
         <v/>
       </c>
       <c r="E7" s="14">
-        <f>E5*'Assumptions'!C144/365</f>
+        <f>E5*'Assumptions'!C149/365</f>
         <v/>
       </c>
       <c r="F7" s="14">
-        <f>F5*'Assumptions'!C144/365</f>
+        <f>F5*'Assumptions'!C149/365</f>
         <v/>
       </c>
     </row>
@@ -1400,23 +1401,23 @@
         </is>
       </c>
       <c r="B8" s="14">
-        <f>B6*'Assumptions'!C145/365</f>
+        <f>B6*'Assumptions'!C150/365</f>
         <v/>
       </c>
       <c r="C8" s="14">
-        <f>C6*'Assumptions'!C145/365</f>
+        <f>C6*'Assumptions'!C150/365</f>
         <v/>
       </c>
       <c r="D8" s="14">
-        <f>D6*'Assumptions'!C145/365</f>
+        <f>D6*'Assumptions'!C150/365</f>
         <v/>
       </c>
       <c r="E8" s="14">
-        <f>E6*'Assumptions'!C145/365</f>
+        <f>E6*'Assumptions'!C150/365</f>
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>F6*'Assumptions'!C145/365</f>
+        <f>F6*'Assumptions'!C150/365</f>
         <v/>
       </c>
     </row>
@@ -1427,23 +1428,23 @@
         </is>
       </c>
       <c r="B9" s="14">
-        <f>B6*'Assumptions'!C146/365</f>
+        <f>B6*'Assumptions'!C151/365</f>
         <v/>
       </c>
       <c r="C9" s="14">
-        <f>C6*'Assumptions'!C146/365</f>
+        <f>C6*'Assumptions'!C151/365</f>
         <v/>
       </c>
       <c r="D9" s="14">
-        <f>D6*'Assumptions'!C146/365</f>
+        <f>D6*'Assumptions'!C151/365</f>
         <v/>
       </c>
       <c r="E9" s="14">
-        <f>E6*'Assumptions'!C146/365</f>
+        <f>E6*'Assumptions'!C151/365</f>
         <v/>
       </c>
       <c r="F9" s="14">
-        <f>F6*'Assumptions'!C146/365</f>
+        <f>F6*'Assumptions'!C151/365</f>
         <v/>
       </c>
     </row>
@@ -1518,23 +1519,23 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="25">
         <f>'DCF'!B14</f>
         <v/>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="25">
         <f>'DCF'!C14</f>
         <v/>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="25">
         <f>'DCF'!D14</f>
         <v/>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <f>'DCF'!E14</f>
         <v/>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="25">
         <f>'DCF'!F14</f>
         <v/>
       </c>
@@ -1733,7 +1734,7 @@
           <t>Full-year project spend at the observed run rate</t>
         </is>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="27">
         <f>B26*4/3</f>
         <v/>
       </c>
@@ -1884,23 +1885,23 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="25">
         <f>'DCF'!B5</f>
         <v/>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <f>'DCF'!C5</f>
         <v/>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <f>'DCF'!D5</f>
         <v/>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <f>'DCF'!E5</f>
         <v/>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <f>'DCF'!F5</f>
         <v/>
       </c>
@@ -1911,23 +1912,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="25">
         <f>'DCF'!B6</f>
         <v/>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <f>'DCF'!C6</f>
         <v/>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <f>'DCF'!D6</f>
         <v/>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <f>'DCF'!E6</f>
         <v/>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <f>'DCF'!F6</f>
         <v/>
       </c>
@@ -1938,23 +1939,23 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="26">
         <f>'DCF'!B7</f>
         <v/>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <f>'DCF'!C7</f>
         <v/>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <f>'DCF'!D7</f>
         <v/>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <f>'DCF'!E7</f>
         <v/>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="26">
         <f>'DCF'!F7</f>
         <v/>
       </c>
@@ -1965,23 +1966,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="25">
         <f>'DCF'!B9</f>
         <v/>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <f>'DCF'!C9</f>
         <v/>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <f>'DCF'!D9</f>
         <v/>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <f>'DCF'!E9</f>
         <v/>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <f>'DCF'!F9</f>
         <v/>
       </c>
@@ -1992,23 +1993,23 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="25">
         <f>'DCF'!B10</f>
         <v/>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="25">
         <f>'DCF'!C10</f>
         <v/>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="25">
         <f>'DCF'!D10</f>
         <v/>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="25">
         <f>'DCF'!E10</f>
         <v/>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="25">
         <f>'DCF'!F10</f>
         <v/>
       </c>
@@ -2019,23 +2020,23 @@
           <t>Capital expenditure</t>
         </is>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="25">
         <f>-'DCF'!B12</f>
         <v/>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="25">
         <f>-'DCF'!C12</f>
         <v/>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="25">
         <f>-'DCF'!D12</f>
         <v/>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="25">
         <f>-'DCF'!E12</f>
         <v/>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="25">
         <f>-'DCF'!F12</f>
         <v/>
       </c>
@@ -2046,23 +2047,23 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="25">
         <f>'DCF'!B14</f>
         <v/>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="25">
         <f>'DCF'!C14</f>
         <v/>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="25">
         <f>'DCF'!D14</f>
         <v/>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="25">
         <f>'DCF'!E14</f>
         <v/>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="25">
         <f>'DCF'!F14</f>
         <v/>
       </c>
@@ -2073,23 +2074,23 @@
           <t>Present value</t>
         </is>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="25">
         <f>'DCF'!B17</f>
         <v/>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="25">
         <f>'DCF'!C17</f>
         <v/>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="25">
         <f>'DCF'!D17</f>
         <v/>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="25">
         <f>'DCF'!E17</f>
         <v/>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="25">
         <f>'DCF'!F17</f>
         <v/>
       </c>
@@ -2100,23 +2101,23 @@
           <t>Urea output (tonnes)</t>
         </is>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="25">
         <f>'Segments'!B5</f>
         <v/>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="25">
         <f>'Segments'!C5</f>
         <v/>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="25">
         <f>'Segments'!D5</f>
         <v/>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <f>'Segments'!E5</f>
         <v/>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <f>'Segments'!F5</f>
         <v/>
       </c>
@@ -2127,23 +2128,23 @@
           <t>Export tonnes</t>
         </is>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="25">
         <f>'Segments'!B9</f>
         <v/>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="25">
         <f>'Segments'!C9</f>
         <v/>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="25">
         <f>'Segments'!D9</f>
         <v/>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <f>'Segments'!E9</f>
         <v/>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="25">
         <f>'Segments'!F9</f>
         <v/>
       </c>
@@ -2154,23 +2155,23 @@
           <t>Export price (US$/t)</t>
         </is>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="31">
         <f>'Assumptions'!C33</f>
         <v/>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <f>'Assumptions'!C34</f>
         <v/>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <f>'Assumptions'!C35</f>
         <v/>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <f>'Assumptions'!C36</f>
         <v/>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <f>'Assumptions'!C37</f>
         <v/>
       </c>
@@ -2238,15 +2239,15 @@
           <t>Revenue — low of the range (EGP m)</t>
         </is>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="25">
         <f>'DCF'!D5*D19</f>
         <v/>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="25">
         <f>'DCF'!E5*E19</f>
         <v/>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="25">
         <f>'DCF'!F5*F19</f>
         <v/>
       </c>
@@ -2257,15 +2258,15 @@
           <t>Revenue — high of the range (EGP m)</t>
         </is>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="25">
         <f>'DCF'!D5*D20</f>
         <v/>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="25">
         <f>'DCF'!E5*E20</f>
         <v/>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="25">
         <f>'DCF'!F5*F20</f>
         <v/>
       </c>
@@ -2724,16 +2725,16 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>-2.64</v>
+        <v>-2.62</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>-2.76</v>
+        <v>-2.74</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>-2.87</v>
+        <v>-2.86</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>-2.94</v>
+        <v>-2.93</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>-3.01</v>
@@ -2746,19 +2747,19 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>-0.41</v>
+        <v>-0.35</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>-0.71</v>
+        <v>-0.66</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>-0.99</v>
+        <v>-0.95</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>-1.18</v>
+        <v>-1.13</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>-1.36</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="8">
@@ -2768,19 +2769,19 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>0.59</v>
+        <v>0.66</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="9">
@@ -2790,19 +2791,19 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>4.04</v>
+        <v>4.19</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>3.38</v>
+        <v>3.52</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="10">
@@ -2812,19 +2813,19 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>6.26</v>
+        <v>6.47</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>5.42</v>
+        <v>5.6</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>4.63</v>
+        <v>4.79</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>4.12</v>
+        <v>4.26</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>3.61</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="11"/>
@@ -2883,11 +2884,11 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>No duty at all (7.8391) or half the rate (6.3691)</t>
+          <t>No duty at all (8.0006) or half the rate (6.5115)</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>7.839130865531535</v>
+        <v>8.000565434916803</v>
       </c>
       <c r="D17" s="11">
         <f>C17-$D$15</f>
@@ -2902,11 +2903,11 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Priced at the SAME PRODUCT'S OWN DISCLOSED REALISED PRICE — EGP 20,000/t from note 20, which is US$408.16/t at this model's FY2024/25 rate of 49.00 (5.4629)</t>
+          <t>Priced at the SAME PRODUCT'S OWN DISCLOSED REALISED PRICE — EGP 20,000/t from note 20, which is US$408.16/t at this model's FY2024/25 rate of 49.00 (5.5970)</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>5.462942564889782</v>
+        <v>5.597036900779846</v>
       </c>
       <c r="D18" s="11">
         <f>C18-$D$15</f>
@@ -2921,11 +2922,11 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Priced off the sovereign's credit rating instead, which is the wider of the two spreads and gives a cost of capital 113 basis points higher</t>
+          <t>Priced off the sovereign's credit rating instead, which is the wider of the two spreads and gives a cost of capital 104 basis points higher</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>3.011321159898108</v>
+        <v>3.102900059761477</v>
       </c>
       <c r="D19" s="11">
         <f>C19-$D$15</f>
@@ -2944,7 +2945,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>1.437646331702388</v>
+        <v>1.47809148744809</v>
       </c>
       <c r="D20" s="11">
         <f>C20-$D$15</f>
@@ -2963,7 +2964,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>2.911296732936654</v>
+        <v>2.980526510171584</v>
       </c>
       <c r="D21" s="11">
         <f>C21-$D$15</f>
@@ -2982,7 +2983,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>3.46502089258036</v>
+        <v>3.548742891573957</v>
       </c>
       <c r="D22" s="11">
         <f>C22-$D$15</f>
@@ -3001,7 +3002,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>7.139227525187105</v>
+        <v>5.899684651558272</v>
       </c>
       <c r="D23" s="11">
         <f>C23-$D$15</f>
@@ -3020,7 +3021,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>1.934303504671326</v>
+        <v>2.020338775157204</v>
       </c>
       <c r="D24" s="11">
         <f>C24-$D$15</f>
@@ -3039,7 +3040,7 @@
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>5.391822837799547</v>
+        <v>5.524568506724146</v>
       </c>
       <c r="D25" s="11">
         <f>C25-$D$15</f>
@@ -3058,7 +3059,7 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>3.983888611941671</v>
+        <v>4.104580574764806</v>
       </c>
       <c r="D26" s="11">
         <f>C26-$D$15</f>
@@ -3077,7 +3078,7 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>2.330018452871625</v>
+        <v>2.404702110064437</v>
       </c>
       <c r="D27" s="11">
         <f>C27-$D$15</f>
@@ -3096,7 +3097,7 @@
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>5.822370305955579</v>
+        <v>5.957407998331238</v>
       </c>
       <c r="D28" s="11">
         <f>C28-$D$15</f>
@@ -3115,7 +3116,7 @@
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>4.694165404333517</v>
+        <v>4.817637069790051</v>
       </c>
       <c r="D29" s="11">
         <f>C29-$D$15</f>
@@ -3233,7 +3234,7 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>'Assumptions'!C100</f>
+        <f>'Assumptions'!C105</f>
         <v/>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -3264,7 +3265,7 @@
           <t>Net debt to EBITDA, FY2026/27</t>
         </is>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <f>'DCF'!B41/'DCF'!B6</f>
         <v/>
       </c>
@@ -3280,7 +3281,7 @@
           <t>Enterprise value to EBITDA at the model's value</t>
         </is>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="27">
         <f>'DCF'!B37/'DCF'!B6</f>
         <v/>
       </c>
@@ -3292,7 +3293,7 @@
           <t>Enterprise value to EBITDA at the market price</t>
         </is>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="27">
         <f>('Summary'!B16+'DCF'!B41)/'DCF'!B6</f>
         <v/>
       </c>
@@ -3861,7 +3862,7 @@
         </is>
       </c>
       <c r="B27" s="16">
-        <f>'Assumptions'!C110</f>
+        <f>'Assumptions'!C115</f>
         <v/>
       </c>
     </row>
@@ -3872,7 +3873,7 @@
         </is>
       </c>
       <c r="B28" s="16">
-        <f>'Assumptions'!C108*'Assumptions'!C99+'Assumptions'!C109*'Assumptions'!C106*(1-'Assumptions'!C107)</f>
+        <f>'Assumptions'!C113*'Assumptions'!C104+'Assumptions'!C114*'Assumptions'!C111*(1-'Assumptions'!C112)</f>
         <v/>
       </c>
     </row>
@@ -3928,7 +3929,7 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>8.985831551431042</v>
+        <v>9.128793547103569</v>
       </c>
     </row>
     <row r="37">
@@ -3949,7 +3950,7 @@
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>6.260028375675609</v>
+        <v>6.315558537881176</v>
       </c>
     </row>
     <row r="39">
@@ -4157,7 +4158,7 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>'Assumptions'!C100</f>
+        <f>'Assumptions'!C105</f>
         <v/>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -4173,7 +4174,7 @@
         </is>
       </c>
       <c r="B15" s="9">
-        <f>'Assumptions'!C117</f>
+        <f>'Assumptions'!C122</f>
         <v/>
       </c>
       <c r="C15" s="10" t="inlineStr"/>
@@ -4270,7 +4271,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>4.899013415739939</v>
+        <v>5.022413776196755</v>
       </c>
     </row>
     <row r="24">
@@ -4280,7 +4281,7 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>8.985831551431042</v>
+        <v>9.128793547103569</v>
       </c>
     </row>
     <row r="25">
@@ -4349,7 +4350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D146"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6136,11 +6137,11 @@
         </is>
       </c>
       <c r="C97" s="21" t="n">
-        <v>1.030210306988178</v>
+        <v>1.01981029917547</v>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>Own-stock weekly regression, 253 observations over 4.9 years against the published EGX30 index (as of 2026-07-22), R-squared 0.250, standard error 0.191, 90% interval 0.72 to 1.34</t>
+          <t>Own-stock weekly regression, 256 observations over 4.9 years against the published EGX30 index (as of 2026-09-08), R-squared 0.248, standard error 0.191, 90% interval 0.71 to 1.33</t>
         </is>
       </c>
     </row>
@@ -6160,250 +6161,238 @@
         <v/>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="24" customHeight="1">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>Cost of equity, rating basis — published, not central</t>
+          <t>Equity-to-bond volatility scaling on the default spread</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C99" s="24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>the ratio of equity volatility to sovereign-bond volatility. It converts a DEBT default spread into the EQUITY country premium, which is the only premium a shareholder is exposed to</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   of which the country premium, rating basis — charged FLAT</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C99" s="16">
-        <f>'Assumptions'!C93+'Assumptions'!C97*'Assumptions'!C94</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t>Cost of equity, CDS basis — THE CENTRAL</t>
-        </is>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="C100" s="16">
+        <f>'Assumptions'!C92*'Assumptions'!C99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   of which the mature equity premium, rating basis</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C100" s="16">
-        <f>'Assumptions'!C98+'Assumptions'!C97*'Assumptions'!C96</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101" ht="24" customHeight="1">
-      <c r="A101" s="7" t="inlineStr">
-        <is>
-          <t>Cost of debt, local currency</t>
-        </is>
-      </c>
-      <c r="B101" s="7" t="inlineStr">
+      <c r="C101" s="16">
+        <f>'Assumptions'!C94-'Assumptions'!C100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   of which the country premium, CDS basis — charged FLAT</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C101" s="23" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="D101" s="10" t="inlineStr">
-        <is>
-          <t>Constructed: EGP 96,896,001 of interest on the EGP 500,000,000 holding-company facility drawn in FY2024/25 — the company's own latest local borrowing</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="14" customHeight="1">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t>Cost of debt, dollar tranche, in dollars</t>
-        </is>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
+      <c r="C102" s="16">
+        <f>'Assumptions'!C95*'Assumptions'!C99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   of which the mature equity premium, CDS basis</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C102" s="23" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="D102" s="10" t="inlineStr">
-        <is>
-          <t>Constructed: EGP 1,338.0m of FY2024/25 interest on a mean dollar balance of about US$233m</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" s="10" t="inlineStr">
-        <is>
-          <t>Terminal currency wedge (the same identity, at the terminal inflation)</t>
-        </is>
-      </c>
-      <c r="B103" s="7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C103" s="23" t="n">
-        <v>0.044921875</v>
-      </c>
-      <c r="D103" s="10" t="inlineStr">
-        <is>
-          <t>Constructed: the central bank's LONG-RUN 5% target against about 2.4% in the United States, on the same relative-purchasing-power identity the study states. CORRECTED 9 August 2026: the study previously asserted 4.5% flat while stating a derivation that produces a different number in every year. The wedge is now computed from the identity rather than asserted, and the currency path is built from it year by year.</t>
-        </is>
+      <c r="C103" s="16">
+        <f>'Assumptions'!C96-'Assumptions'!C102</f>
+        <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
+          <t>Cost of equity, rating basis — published, not central</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C104" s="16">
+        <f>'Assumptions'!C93+'Assumptions'!C97*'Assumptions'!C101+'Assumptions'!C100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>Cost of equity, CDS basis — THE CENTRAL</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C105" s="16">
+        <f>'Assumptions'!C98+'Assumptions'!C97*'Assumptions'!C103+'Assumptions'!C102</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" ht="24" customHeight="1">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>Cost of debt, local currency</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C106" s="23" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>Constructed: EGP 96,896,001 of interest on the EGP 500,000,000 holding-company facility drawn in FY2024/25 — the company's own latest local borrowing</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="14" customHeight="1">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>Cost of debt, dollar tranche, in dollars</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C107" s="23" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>Constructed: EGP 1,338.0m of FY2024/25 interest on a mean dollar balance of about US$233m</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>Terminal currency wedge (the same identity, at the terminal inflation)</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C108" s="23" t="n">
+        <v>0.044921875</v>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>Constructed: the central bank's LONG-RUN 5% target against about 2.4% in the United States, on the same relative-purchasing-power identity the study states. CORRECTED 9 August 2026: the study previously asserted 4.5% flat while stating a derivation that produces a different number in every year. The wedge is now computed from the identity rather than asserted, and the currency path is built from it year by year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
           <t>Dollar debt at local-equivalent cost, year one (FY2026/27 wedge)</t>
         </is>
       </c>
-      <c r="B104" s="7" t="inlineStr">
+      <c r="B109" s="7" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C104" s="16">
-        <f>(1+'Assumptions'!C102)*(1+'Assumptions'!C40)-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105" ht="24" customHeight="1">
-      <c r="A105" s="7" t="inlineStr">
+      <c r="C109" s="16">
+        <f>(1+'Assumptions'!C107)*(1+'Assumptions'!C40)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" ht="24" customHeight="1">
+      <c r="A110" s="7" t="inlineStr">
         <is>
           <t>Share of debt in local currency</t>
         </is>
       </c>
-      <c r="B105" s="7" t="inlineStr">
+      <c r="B110" s="7" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C105" s="15" t="n">
+      <c r="C110" s="15" t="n">
         <v>0.003139216087432172</v>
       </c>
-      <c r="D105" s="10" t="inlineStr">
+      <c r="D110" s="10" t="inlineStr">
         <is>
           <t>The pound tranche of the project loan was repaid in June 2024, so the book is almost entirely dollar</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="7" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
         <is>
           <t>Blended pre-tax cost of debt</t>
         </is>
       </c>
-      <c r="B106" s="7" t="inlineStr">
+      <c r="B111" s="7" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C106" s="16">
-        <f>'Assumptions'!C105*'Assumptions'!C101+(1-'Assumptions'!C105)*'Assumptions'!C104</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107" ht="24" customHeight="1">
-      <c r="A107" s="7" t="inlineStr">
-        <is>
-          <t>Tax rate</t>
-        </is>
-      </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C107" s="15" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="D107" s="10" t="inlineStr">
-        <is>
-          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 5-16 income tax</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="14" customHeight="1">
-      <c r="A108" s="7" t="inlineStr">
-        <is>
-          <t>Equity weight</t>
-        </is>
-      </c>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C108" s="15" t="n">
-        <v>0.6616480028913871</v>
-      </c>
-      <c r="D108" s="10" t="inlineStr">
-        <is>
-          <t>Market-value equity over market-value equity plus debt</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="14" customHeight="1">
-      <c r="A109" s="7" t="inlineStr">
-        <is>
-          <t>Debt weight</t>
-        </is>
-      </c>
-      <c r="B109" s="7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C109" s="15" t="n">
-        <v>0.3383519971086129</v>
-      </c>
-      <c r="D109" s="10" t="inlineStr">
-        <is>
-          <t>One less the equity weight</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="7" t="inlineStr">
-        <is>
-          <t>Cost of capital, year one</t>
-        </is>
-      </c>
-      <c r="B110" s="7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C110" s="16">
-        <f>'Assumptions'!C108*'Assumptions'!C100+'Assumptions'!C109*'Assumptions'!C106*(1-'Assumptions'!C107)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111" ht="108" customHeight="1">
-      <c r="A111" s="10" t="inlineStr">
-        <is>
-          <t>Terminal inflation (the same figure terminal growth is set at)</t>
-        </is>
-      </c>
-      <c r="B111" s="7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C111" s="15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D111" s="10" t="inlineStr">
-        <is>
-          <t>The inflation embedded in the TERMINAL discount rate, taken from the house macro path and NOT typed here — the SAME figure terminal growth is set at, so the two cannot drift apart. (This sentence previously described the value as 5%, the central bank's Q4-2028 target, while the path supplies 7%: a 7% value carrying a 5% justification, which is exactly the kind of unfalsifiable typed rate this series does not permit. The value has always come from the path; only the sentence was wrong.) CORRECTED 1 September 2026: the 08-08-2026 edition built the terminal risk-free rate on the 7% Q4-2026 target while growing the perpetuity at 5%, a perpetual real decline of about 2% a year that no disclosure supports (the same defect the AMOC review found, L-055). Terminal growth, the terminal risk-free rate and the terminal currency wedge now share one inflation.</t>
-        </is>
+      <c r="C111" s="16">
+        <f>'Assumptions'!C110*'Assumptions'!C106+(1-'Assumptions'!C110)*'Assumptions'!C109</f>
+        <v/>
       </c>
     </row>
     <row r="112" ht="24" customHeight="1">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>Long-run real rate</t>
+          <t>Tax rate</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -6412,18 +6401,18 @@
         </is>
       </c>
       <c r="C112" s="15" t="n">
-        <v>0.035</v>
+        <v>0.225</v>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>The house real-rate convention, used to build the terminal risk-free rate from its own components rather than from a spot yield</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="10" t="inlineStr">
-        <is>
-          <t>Terminal normalised risk-free rate — terminal inflation plus the long-run real rate, on the house macro path's own construction</t>
+          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 5-16 income tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="14" customHeight="1">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>Equity weight</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -6431,15 +6420,19 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C113" s="16">
-        <f>'Assumptions'!C111+'Assumptions'!C112</f>
-        <v/>
+      <c r="C113" s="15" t="n">
+        <v>0.6616480028913871</v>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>Market-value equity over market-value equity plus debt</t>
+        </is>
       </c>
     </row>
     <row r="114" ht="14" customHeight="1">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>Long-run dollar cost of debt</t>
+          <t>Debt weight</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -6447,615 +6440,707 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C114" s="23" t="n">
-        <v>0.09</v>
+      <c r="C114" s="15" t="n">
+        <v>0.3383519971086129</v>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Constructed: long-run corporate dollar cost of debt</t>
+          <t>One less the equity weight</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
+          <t>Cost of capital, year one</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C115" s="16">
+        <f>'Assumptions'!C113*'Assumptions'!C105+'Assumptions'!C114*'Assumptions'!C111*(1-'Assumptions'!C112)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" ht="108" customHeight="1">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
+          <t>Terminal inflation (the same figure terminal growth is set at)</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C116" s="15" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D116" s="10" t="inlineStr">
+        <is>
+          <t>The inflation embedded in the TERMINAL discount rate, taken from the house macro path and NOT typed here — the SAME figure terminal growth is set at, so the two cannot drift apart. (This sentence previously described the value as 5%, the central bank's Q4-2028 target, while the path supplies 7%: a 7% value carrying a 5% justification, which is exactly the kind of unfalsifiable typed rate this series does not permit. The value has always come from the path; only the sentence was wrong.) CORRECTED 1 September 2026: the 08-08-2026 edition built the terminal risk-free rate on the 7% Q4-2026 target while growing the perpetuity at 5%, a perpetual real decline of about 2% a year that no disclosure supports (the same defect the AMOC review found, L-055). Terminal growth, the terminal risk-free rate and the terminal currency wedge now share one inflation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="24" customHeight="1">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>Long-run real rate</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C117" s="15" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D117" s="10" t="inlineStr">
+        <is>
+          <t>The house real-rate convention, used to build the terminal risk-free rate from its own components rather than from a spot yield</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>Terminal normalised risk-free rate — terminal inflation plus the long-run real rate, on the house macro path's own construction</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C118" s="16">
+        <f>'Assumptions'!C116+'Assumptions'!C117</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" ht="14" customHeight="1">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>Long-run dollar cost of debt</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C119" s="23" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>Constructed: long-run corporate dollar cost of debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
           <t>Terminal cost of debt, local-equivalent</t>
         </is>
       </c>
-      <c r="B115" s="7" t="inlineStr">
+      <c r="B120" s="7" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C115" s="16">
-        <f>'Assumptions'!C105*'Assumptions'!C101+(1-'Assumptions'!C105)*((1+'Assumptions'!C114)*(1+'Assumptions'!C103)-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="7" t="inlineStr">
+      <c r="C120" s="16">
+        <f>'Assumptions'!C110*'Assumptions'!C106+(1-'Assumptions'!C110)*((1+'Assumptions'!C119)*(1+'Assumptions'!C108)-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
         <is>
           <t>TERMINAL COST OF CAPITAL</t>
         </is>
       </c>
-      <c r="B116" s="7" t="inlineStr">
+      <c r="B121" s="7" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C116" s="16">
-        <f>'Assumptions'!C108*('Assumptions'!C113+'Assumptions'!C97*'Assumptions'!C96)+'Assumptions'!C109*'Assumptions'!C115*(1-'Assumptions'!C107)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="117" ht="72" customHeight="1">
-      <c r="A117" s="7" t="inlineStr">
+      <c r="C121" s="16">
+        <f>'Assumptions'!C113*('Assumptions'!C118+'Assumptions'!C97*'Assumptions'!C103+'Assumptions'!C102)+'Assumptions'!C114*'Assumptions'!C120*(1-'Assumptions'!C112)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" ht="72" customHeight="1">
+      <c r="A122" s="7" t="inlineStr">
         <is>
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="B117" s="7" t="inlineStr">
+      <c r="B122" s="7" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C117" s="15" t="n">
+      <c r="C122" s="15" t="n">
         <v>0.07000000000000006</v>
       </c>
-      <c r="D117" s="10" t="inlineStr">
+      <c r="D122" s="10" t="inlineStr">
         <is>
           <t>Terminal growth from the house macro path: terminal inflation plus a STATED real growth of zero, so the real assumption is written down rather than inferred from the gap to the discount rate. It was 5% (+/-2) for Q4 2028. CORRECTED 9 August 2026 after external critique: the study previously used the 7% Q4-2026 target, which expires one quarter after the anchor date, as a perpetuity anchor -- and then defended it by calling 5% 'below the target', inverting the central bank's own target structure. A perpetuity takes the longest-horizon target there is.</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="132" customHeight="1">
-      <c r="A118" s="7" t="inlineStr">
+    <row r="123" ht="132" customHeight="1">
+      <c r="A123" s="7" t="inlineStr">
         <is>
           <t>Average age of the fixed-asset base — MEASURED</t>
         </is>
       </c>
-      <c r="B118" s="7" t="inlineStr">
+      <c r="B123" s="7" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="C118" s="12" t="n">
+      <c r="C123" s="12" t="n">
         <v>4.454408352548927</v>
       </c>
-      <c r="D118" s="10" t="inlineStr">
+      <c r="D123" s="10" t="inlineStr">
         <is>
           <t>DERIVED BY IDENTITY, labelled as derived: accumulated depreciation over the year's own charge. Under straight-line depreciation accumulated equals age times charge, so the ratio is the charge-weighted average age of the base. THE THREE CONDITIONS THAT BREAK THAT IDENTITY ARE CHECKED AND CLEAR HERE. There is no residual value: the policy note writes off cost over the useful life and mentions none. No useful life has been reassessed: the disclosed rates are unchanged from the prior year's identical table. And the base was not assembled by acquisition — it is one plant, built and extended by this company. The corroboration is that only EGP 220mn, 1.3% of the base, is fully depreciated and still in production, so almost nothing is past its accounting life and the gross-over-charge life below reads close to a true weighted life rather than a longer economic cycle. 4.45 years against the 11.04 that half of that life would assume: this plant was rebuilt recently and has another complex still under construction.</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="84" customHeight="1">
-      <c r="A119" s="7" t="inlineStr">
+    <row r="124" ht="84" customHeight="1">
+      <c r="A124" s="7" t="inlineStr">
         <is>
           <t>Replacement cycle the accounts imply</t>
         </is>
       </c>
-      <c r="B119" s="7" t="inlineStr">
+      <c r="B124" s="7" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="C119" s="12" t="n">
+      <c r="C124" s="12" t="n">
         <v>22.07019266619699</v>
       </c>
-      <c r="D119" s="10" t="inlineStr">
+      <c r="D124" s="10" t="inlineStr">
         <is>
           <t>DERIVED BY IDENTITY, labelled as derived: the depreciable gross cost — cost less land, which is never depreciated — over the year's own charge. It is the replacement cycle the accounts themselves run, and it sits inside the disclosed range: note 5-2 gives 3.95% on the urea and ammonia machinery (25.3 years), 9.5% on the factories (10.5), 6.5% on the workshops (15.4), 6% on the factory buildings (16.7), 2 to 5% on the residential city and the water and sewage pipes (20 to 50) and 4.75% on the intangible (21.1). A weighted life cannot be read off the note because it publishes no class balances, so the identity supplies one and the disclosed range is what checks it.</t>
         </is>
       </c>
     </row>
-    <row r="120"/>
-    <row r="121">
-      <c r="A121" s="19" t="inlineStr">
+    <row r="125"/>
+    <row r="126">
+      <c r="A126" s="19" t="inlineStr">
         <is>
           <t>CAPITAL, WORKING CAPITAL AND THE PROJECT</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="24" customHeight="1">
-      <c r="A122" s="7" t="inlineStr">
+    <row r="127" ht="24" customHeight="1">
+      <c r="A127" s="7" t="inlineStr">
         <is>
           <t>Depreciation charge, FY2024/25</t>
         </is>
       </c>
-      <c r="B122" s="7" t="inlineStr">
+      <c r="B127" s="7" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C122" s="20" t="n">
+      <c r="C127" s="20" t="n">
         <v>771.213</v>
       </c>
-      <c r="D122" s="10" t="inlineStr">
+      <c r="D127" s="10" t="inlineStr">
         <is>
           <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 6 fixed-asset register</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="24" customHeight="1">
-      <c r="A123" s="7" t="inlineStr">
+    <row r="128" ht="24" customHeight="1">
+      <c r="A128" s="7" t="inlineStr">
         <is>
           <t>Amortisation, FY2024/25</t>
         </is>
       </c>
-      <c r="B123" s="7" t="inlineStr">
+      <c r="B128" s="7" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C123" s="20" t="n">
+      <c r="C128" s="20" t="n">
         <v>119.378</v>
       </c>
-      <c r="D123" s="10" t="inlineStr">
+      <c r="D128" s="10" t="inlineStr">
         <is>
           <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 10 usufruct intangible</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" s="7" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" s="7" t="inlineStr">
         <is>
           <t>Project capital expenditure — FY2026/27</t>
         </is>
       </c>
-      <c r="B124" s="7" t="inlineStr">
+      <c r="B129" s="7" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C124" s="14">
+      <c r="C129" s="14">
         <f>'Cash Flow'!B30</f>
         <v/>
       </c>
-      <c r="D124" s="10" t="inlineStr">
+      <c r="D129" s="10" t="inlineStr">
         <is>
           <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" s="7" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" s="7" t="inlineStr">
         <is>
           <t>Project capital expenditure — FY2027/28</t>
         </is>
       </c>
-      <c r="B125" s="7" t="inlineStr">
+      <c r="B130" s="7" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C125" s="13" t="n">
+      <c r="C130" s="13" t="n">
         <v>3100</v>
       </c>
-      <c r="D125" s="10" t="inlineStr">
+      <c r="D130" s="10" t="inlineStr">
         <is>
           <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" s="7" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" s="7" t="inlineStr">
         <is>
           <t>Project capital expenditure — FY2028/29</t>
         </is>
       </c>
-      <c r="B126" s="7" t="inlineStr">
+      <c r="B131" s="7" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C126" s="13" t="n">
+      <c r="C131" s="13" t="n">
         <v>3300</v>
       </c>
-      <c r="D126" s="10" t="inlineStr">
+      <c r="D131" s="10" t="inlineStr">
         <is>
           <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" s="7" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" s="7" t="inlineStr">
         <is>
           <t>Project capital expenditure — FY2029/30</t>
         </is>
       </c>
-      <c r="B127" s="7" t="inlineStr">
+      <c r="B132" s="7" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C127" s="13" t="n">
+      <c r="C132" s="13" t="n">
         <v>3200</v>
       </c>
-      <c r="D127" s="10" t="inlineStr">
+      <c r="D132" s="10" t="inlineStr">
         <is>
           <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" s="7" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" s="7" t="inlineStr">
         <is>
           <t>Project capital expenditure — FY2030/31</t>
         </is>
       </c>
-      <c r="B128" s="7" t="inlineStr">
+      <c r="B133" s="7" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C128" s="14">
-        <f>'Cash Flow'!D34-(C124+C125+C126+C127)</f>
-        <v/>
-      </c>
-      <c r="D128" s="10" t="inlineStr">
+      <c r="C133" s="14">
+        <f>'Cash Flow'!D34-(C129+C130+C131+C132)</f>
+        <v/>
+      </c>
+      <c r="D133" s="10" t="inlineStr">
         <is>
           <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="24" customHeight="1">
-      <c r="A129" s="7" t="inlineStr">
+    <row r="134" ht="24" customHeight="1">
+      <c r="A134" s="7" t="inlineStr">
         <is>
           <t>Depreciation escalation on the existing base</t>
         </is>
       </c>
-      <c r="B129" s="7" t="inlineStr">
+      <c r="B134" s="7" t="inlineStr">
         <is>
           <t>per year</t>
         </is>
       </c>
-      <c r="C129" s="15" t="n">
+      <c r="C134" s="15" t="n">
         <v>0.02</v>
       </c>
-      <c r="D129" s="10" t="inlineStr">
+      <c r="D134" s="10" t="inlineStr">
         <is>
           <t>Constructed: escalation on the existing depreciation base, reflecting ordinary additions to the plant already in service</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="24" customHeight="1">
-      <c r="A130" s="7" t="inlineStr">
+    <row r="135" ht="24" customHeight="1">
+      <c r="A135" s="7" t="inlineStr">
         <is>
           <t>Depreciation rate on the new complex</t>
         </is>
       </c>
-      <c r="B130" s="7" t="inlineStr">
+      <c r="B135" s="7" t="inlineStr">
         <is>
           <t>per year</t>
         </is>
       </c>
-      <c r="C130" s="23" t="n">
+      <c r="C135" s="23" t="n">
         <v>0.0395</v>
       </c>
-      <c r="D130" s="10" t="inlineStr">
+      <c r="D135" s="10" t="inlineStr">
         <is>
           <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 5-2 depreciation rates</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="48" customHeight="1">
-      <c r="A131" s="7" t="inlineStr">
+    <row r="136" ht="48" customHeight="1">
+      <c r="A136" s="7" t="inlineStr">
         <is>
           <t>New complex nameplate</t>
         </is>
       </c>
-      <c r="B131" s="7" t="inlineStr">
+      <c r="B136" s="7" t="inlineStr">
         <is>
           <t>tonnes/day</t>
         </is>
       </c>
-      <c r="C131" s="13" t="n">
+      <c r="C136" s="13" t="n">
         <v>800</v>
       </c>
-      <c r="D131" s="10" t="inlineStr">
+      <c r="D136" s="10" t="inlineStr">
         <is>
           <t>EPC award for this plant (Tecnimont S.p.A. with Orascom Construction, announced 9 June 2023): 600 t/day nitric acid converted to 800 t/day of fertilizer-grade granulated ammonium nitrate. FOUND BY EXTERNAL CRITIQUE 9 August 2026 -- the study had said 'no filing states it' and derived the plate from the ammonia surplus instead.</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="24" customHeight="1">
-      <c r="A132" s="7" t="inlineStr">
+    <row r="137" ht="24" customHeight="1">
+      <c r="A137" s="7" t="inlineStr">
         <is>
           <t>Operating days a year</t>
         </is>
       </c>
-      <c r="B132" s="7" t="inlineStr">
+      <c r="B137" s="7" t="inlineStr">
         <is>
           <t>days</t>
         </is>
       </c>
-      <c r="C132" s="13" t="n">
+      <c r="C137" s="13" t="n">
         <v>330</v>
       </c>
-      <c r="D132" s="10" t="inlineStr">
+      <c r="D137" s="10" t="inlineStr">
         <is>
           <t>Constructed: operating days a year for a continuous nitrate line, net of the turnaround the company takes annually</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="48" customHeight="1">
-      <c r="A133" s="10" t="inlineStr">
+    <row r="138" ht="48" customHeight="1">
+      <c r="A138" s="10" t="inlineStr">
         <is>
           <t>Steady-state depreciation wedge in the terminal year</t>
         </is>
       </c>
-      <c r="B133" s="7" t="inlineStr">
+      <c r="B138" s="7" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="C133" s="15" t="n">
+      <c r="C138" s="15" t="n">
         <v>0.025390625</v>
       </c>
-      <c r="D133" s="10" t="inlineStr">
+      <c r="D138" s="10" t="inlineStr">
         <is>
           <t>DERIVED: the steady-state currency depreciation the terminal inflation (5%) implies against long-run US inflation (2.4%) on the relative purchasing-power identity — the same wedge that carries the dollar debt in the terminal year. RE-SET 1 September 2026 from a typed 2.5% so that the terminal currency, the terminal cost of debt and the last explicit year share one number.</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="24" customHeight="1">
-      <c r="A134" s="10" t="inlineStr">
+    <row r="139" ht="24" customHeight="1">
+      <c r="A139" s="10" t="inlineStr">
         <is>
           <t>The complex is completed and in service (1 = yes)</t>
         </is>
       </c>
-      <c r="B134" s="7" t="inlineStr">
+      <c r="B139" s="7" t="inlineStr">
         <is>
           <t>switch</t>
         </is>
       </c>
-      <c r="C134" s="13" t="n">
+      <c r="C139" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D134" s="10" t="inlineStr">
+      <c r="D139" s="10" t="inlineStr">
         <is>
           <t>Case switch. Zero in the capital-discipline column, where the plant is never finished and therefore never depreciated.</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="36" customHeight="1">
-      <c r="A135" s="7" t="inlineStr">
+    <row r="140" ht="36" customHeight="1">
+      <c r="A140" s="7" t="inlineStr">
         <is>
           <t>Approved cost of the new complex</t>
         </is>
       </c>
-      <c r="B135" s="7" t="inlineStr">
+      <c r="B140" s="7" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C135" s="13" t="n">
+      <c r="C140" s="13" t="n">
         <v>20341.668</v>
       </c>
-      <c r="D135" s="10" t="inlineStr">
+      <c r="D140" s="10" t="inlineStr">
         <is>
           <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 18-3 — bank-approved investment cost, agreement of 25 June 2025; dual-currency tranches at the approval rate</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="72" customHeight="1">
-      <c r="A136" s="7" t="inlineStr">
+    <row r="141" ht="72" customHeight="1">
+      <c r="A141" s="7" t="inlineStr">
         <is>
           <t>Maintenance capital expenditure</t>
         </is>
       </c>
-      <c r="B136" s="7" t="inlineStr">
+      <c r="B141" s="7" t="inlineStr">
         <is>
           <t>% of revenue</t>
         </is>
       </c>
-      <c r="C136" s="9">
+      <c r="C141" s="9">
         <f>'Cash Flow'!D28</f>
         <v/>
       </c>
-      <c r="D136" s="10" t="inlineStr">
+      <c r="D141" s="10" t="inlineStr">
         <is>
           <t>Maintenance capital expenditure as a share of revenue, RE-ANCHORED 9 August 2026 on the company's OWN pre-project cash-flow statements: EGP 123.3m spent across FY2021/22 and FY2022/23 on EGP 11,052.9m of revenue. The first issue of this study used a 3.0% mature-plant standard instead, which is 2.7 times what this company has ever spent to keep its plant running, and which no disclosure supports. The replacement-rate framing (gross fixed assets at the disclosed 3.95% machinery rate, 6.11% of revenue) is carried as the published alternative and as the downside case.</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="36" customHeight="1">
-      <c r="A137" s="7" t="inlineStr">
+    <row r="142" ht="36" customHeight="1">
+      <c r="A142" s="7" t="inlineStr">
         <is>
           <t>Wind-down cost if the programme is stopped</t>
         </is>
       </c>
-      <c r="B137" s="7" t="inlineStr">
+      <c r="B142" s="7" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C137" s="13" t="n">
+      <c r="C142" s="13" t="n">
         <v>1000</v>
       </c>
-      <c r="D137" s="10" t="inlineStr">
+      <c r="D142" s="10" t="inlineStr">
         <is>
           <t>Constructed: capital-discipline case only: the cost of stopping the programme in the first forecast year — contract settlement and site preservation. No filing states it; it is the study's estimate and is flagged.</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="24" customHeight="1">
-      <c r="A138" s="7" t="inlineStr">
+    <row r="143" ht="24" customHeight="1">
+      <c r="A143" s="7" t="inlineStr">
         <is>
           <t>Ammonia per tonne of nitrate</t>
         </is>
       </c>
-      <c r="B138" s="7" t="inlineStr">
+      <c r="B143" s="7" t="inlineStr">
         <is>
           <t>tonnes</t>
         </is>
       </c>
-      <c r="C138" s="12" t="n">
+      <c r="C143" s="12" t="n">
         <v>0.43</v>
       </c>
-      <c r="D138" s="10" t="inlineStr">
+      <c r="D143" s="10" t="inlineStr">
         <is>
           <t>Constructed: ammonia per tonne of ammonium nitrate through the nitric-acid route plus direct neutralisation</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="40" customHeight="1">
-      <c r="A139" s="7" t="inlineStr">
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" s="7" t="inlineStr">
         <is>
           <t>Project nameplate (derived, not disclosed)</t>
         </is>
       </c>
-      <c r="B139" s="7" t="inlineStr">
+      <c r="B144" s="7" t="inlineStr">
         <is>
           <t>tonnes/year</t>
         </is>
       </c>
-      <c r="C139" s="14">
-        <f>'Assumptions'!C131*'Assumptions'!C132</f>
-        <v/>
-      </c>
-      <c r="D139" s="10" t="inlineStr">
+      <c r="C144" s="14">
+        <f>'Assumptions'!C136*'Assumptions'!C137</f>
+        <v/>
+      </c>
+      <c r="D144" s="10" t="inlineStr">
         <is>
           <t>EPC award for this plant (Tecnimont S.p.A. with Orascom Construction, announced 9 June 2023): 600 t/day nitric acid converted to 800 t/day of fertilizer-grade granulated ammonium nitrate. FOUND BY EXTERNAL CRITIQUE 9 August 2026 -- the study had said 'no filing states it' and derived the plate from the ammonia surplus instead.</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="40" customHeight="1">
-      <c r="A140" s="10" t="inlineStr">
+    <row r="145" ht="40" customHeight="1">
+      <c r="A145" s="10" t="inlineStr">
         <is>
           <t>Cross-check: nameplate derived from the ammonia surplus</t>
         </is>
       </c>
-      <c r="B140" s="7" t="inlineStr">
+      <c r="B145" s="7" t="inlineStr">
         <is>
           <t>tonnes/year</t>
         </is>
       </c>
-      <c r="C140" s="14">
-        <f>('Assumptions'!C14-'Assumptions'!C13*'Assumptions'!C15)/'Assumptions'!C138</f>
-        <v/>
-      </c>
-      <c r="D140" s="10" t="inlineStr">
+      <c r="C145" s="14">
+        <f>('Assumptions'!C14-'Assumptions'!C13*'Assumptions'!C15)/'Assumptions'!C143</f>
+        <v/>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
         <is>
           <t>The construction the study used before the engineering award was found. Retained as a cross-check on the disclosed plate, not as the plate itself.</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="14" customHeight="1">
-      <c r="A141" s="7" t="inlineStr">
-        <is>
-          <t>Project utilisation in the terminal year</t>
-        </is>
-      </c>
-      <c r="B141" s="7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C141" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D141" s="10" t="inlineStr">
-        <is>
-          <t>Constructed: project utilisation in the terminal year, central case</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="14" customHeight="1">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t>Nitrate price</t>
-        </is>
-      </c>
-      <c r="B142" s="7" t="inlineStr">
-        <is>
-          <t>US$/tonne</t>
-        </is>
-      </c>
-      <c r="C142" s="13" t="n">
-        <v>280</v>
-      </c>
-      <c r="D142" s="10" t="inlineStr">
-        <is>
-          <t>Mid-cycle ammonium nitrate pricing</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="14" customHeight="1">
-      <c r="A143" s="7" t="inlineStr">
-        <is>
-          <t>Project cash margin</t>
-        </is>
-      </c>
-      <c r="B143" s="7" t="inlineStr">
-        <is>
-          <t>% of revenue</t>
-        </is>
-      </c>
-      <c r="C143" s="15" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="D143" s="10" t="inlineStr">
-        <is>
-          <t>Constructed: conversion margin on ammonium nitrate over its own ammonia feedstock</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="14" customHeight="1">
-      <c r="A144" s="7" t="inlineStr">
-        <is>
-          <t>Days sales outstanding</t>
-        </is>
-      </c>
-      <c r="B144" s="7" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="C144" s="20" t="n">
-        <v>26.77469536556713</v>
-      </c>
-      <c r="D144" s="10" t="inlineStr">
-        <is>
-          <t>Constructed: FY2024/25 receivables over revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="14" customHeight="1">
-      <c r="A145" s="7" t="inlineStr">
-        <is>
-          <t>Days inventory outstanding</t>
-        </is>
-      </c>
-      <c r="B145" s="7" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="C145" s="20" t="n">
-        <v>165.2475279747788</v>
-      </c>
-      <c r="D145" s="10" t="inlineStr">
-        <is>
-          <t>Constructed: FY2024/25 inventory over cost of sales</t>
         </is>
       </c>
     </row>
     <row r="146" ht="14" customHeight="1">
       <c r="A146" s="7" t="inlineStr">
         <is>
+          <t>Project utilisation in the terminal year</t>
+        </is>
+      </c>
+      <c r="B146" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C146" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D146" s="10" t="inlineStr">
+        <is>
+          <t>Constructed: project utilisation in the terminal year, central case</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="14" customHeight="1">
+      <c r="A147" s="7" t="inlineStr">
+        <is>
+          <t>Nitrate price</t>
+        </is>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>US$/tonne</t>
+        </is>
+      </c>
+      <c r="C147" s="13" t="n">
+        <v>280</v>
+      </c>
+      <c r="D147" s="10" t="inlineStr">
+        <is>
+          <t>Mid-cycle ammonium nitrate pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="14" customHeight="1">
+      <c r="A148" s="7" t="inlineStr">
+        <is>
+          <t>Project cash margin</t>
+        </is>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>% of revenue</t>
+        </is>
+      </c>
+      <c r="C148" s="15" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D148" s="10" t="inlineStr">
+        <is>
+          <t>Constructed: conversion margin on ammonium nitrate over its own ammonia feedstock</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="14" customHeight="1">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>Days sales outstanding</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="C149" s="20" t="n">
+        <v>26.77469536556713</v>
+      </c>
+      <c r="D149" s="10" t="inlineStr">
+        <is>
+          <t>Constructed: FY2024/25 receivables over revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="14" customHeight="1">
+      <c r="A150" s="7" t="inlineStr">
+        <is>
+          <t>Days inventory outstanding</t>
+        </is>
+      </c>
+      <c r="B150" s="7" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="C150" s="20" t="n">
+        <v>165.2475279747788</v>
+      </c>
+      <c r="D150" s="10" t="inlineStr">
+        <is>
+          <t>Constructed: FY2024/25 inventory over cost of sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="14" customHeight="1">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
           <t>Days payable outstanding</t>
         </is>
       </c>
-      <c r="B146" s="7" t="inlineStr">
+      <c r="B151" s="7" t="inlineStr">
         <is>
           <t>days</t>
         </is>
       </c>
-      <c r="C146" s="20" t="n">
+      <c r="C151" s="20" t="n">
         <v>83.17161071710899</v>
       </c>
-      <c r="D146" s="10" t="inlineStr">
+      <c r="D151" s="10" t="inlineStr">
         <is>
           <t>Constructed: FY2024/25 payables over cost of sales</t>
         </is>
@@ -7125,11 +7210,11 @@
           <t>Present value of the explicit window</t>
         </is>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="25">
         <f>'DCF'!B36</f>
         <v/>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <f>'DCF'!D36</f>
         <v/>
       </c>
@@ -7145,11 +7230,11 @@
           <t>Present value of the terminal value</t>
         </is>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="25">
         <f>'DCF'!B33</f>
         <v/>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <f>'DCF'!D33</f>
         <v/>
       </c>
@@ -7165,11 +7250,11 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="25">
         <f>'DCF'!B37</f>
         <v/>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <f>'DCF'!D37</f>
         <v/>
       </c>
@@ -7181,11 +7266,11 @@
           <t>Terminal value as a share of enterprise value</t>
         </is>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="26">
         <f>'DCF'!B38</f>
         <v/>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <f>'DCF'!D38</f>
         <v/>
       </c>
@@ -7201,11 +7286,11 @@
           <t>Less net debt</t>
         </is>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="25">
         <f>-'DCF'!B41</f>
         <v/>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="25">
         <f>-'DCF'!D41</f>
         <v/>
       </c>
@@ -7221,11 +7306,11 @@
           <t>Plus listed equity stakes at market</t>
         </is>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="25">
         <f>'DCF'!B42</f>
         <v/>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="25">
         <f>'DCF'!D42</f>
         <v/>
       </c>
@@ -7241,11 +7326,11 @@
           <t>Plus investment property</t>
         </is>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="25">
         <f>'DCF'!B43</f>
         <v/>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="25">
         <f>'DCF'!D43</f>
         <v/>
       </c>
@@ -7261,11 +7346,11 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="25">
         <f>'DCF'!B45</f>
         <v/>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="25">
         <f>'DCF'!D45</f>
         <v/>
       </c>
@@ -7904,23 +7989,23 @@
         </is>
       </c>
       <c r="B25" s="14">
-        <f>'Assumptions'!C122*(1+'Assumptions'!C129*0)+'Assumptions'!C123</f>
+        <f>'Assumptions'!C127*(1+'Assumptions'!C134*0)+'Assumptions'!C128</f>
         <v/>
       </c>
       <c r="C25" s="14">
-        <f>'Assumptions'!C122*(1+'Assumptions'!C129*1)+'Assumptions'!C123+SUM('Assumptions'!C124:C124)*'Assumptions'!C130</f>
+        <f>'Assumptions'!C127*(1+'Assumptions'!C134*1)+'Assumptions'!C128+SUM('Assumptions'!C129:C129)*'Assumptions'!C135</f>
         <v/>
       </c>
       <c r="D25" s="14">
-        <f>'Assumptions'!C122*(1+'Assumptions'!C129*2)+'Assumptions'!C123+SUM('Assumptions'!C124:C125)*'Assumptions'!C130</f>
+        <f>'Assumptions'!C127*(1+'Assumptions'!C134*2)+'Assumptions'!C128+SUM('Assumptions'!C129:C130)*'Assumptions'!C135</f>
         <v/>
       </c>
       <c r="E25" s="14">
-        <f>'Assumptions'!C122*(1+'Assumptions'!C129*3)+'Assumptions'!C123+SUM('Assumptions'!C124:C126)*'Assumptions'!C130</f>
+        <f>'Assumptions'!C127*(1+'Assumptions'!C134*3)+'Assumptions'!C128+SUM('Assumptions'!C129:C131)*'Assumptions'!C135</f>
         <v/>
       </c>
       <c r="F25" s="14">
-        <f>'Assumptions'!C122*(1+'Assumptions'!C129*4)+'Assumptions'!C123+SUM('Assumptions'!C124:C127)*'Assumptions'!C130</f>
+        <f>'Assumptions'!C127*(1+'Assumptions'!C134*4)+'Assumptions'!C128+SUM('Assumptions'!C129:C132)*'Assumptions'!C135</f>
         <v/>
       </c>
     </row>
@@ -8306,7 +8391,7 @@
           <t>Mid-point</t>
         </is>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="27">
         <f>(B6+B7)/2</f>
         <v/>
       </c>
@@ -8398,7 +8483,7 @@
           <t>Multiple the market pays</t>
         </is>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="27">
         <f>('Summary'!B16+'DCF'!B41)/B5</f>
         <v/>
       </c>
@@ -8414,7 +8499,7 @@
           <t>Multiple this model's cash-flow lens implies</t>
         </is>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="27">
         <f>'DCF'!B37/B5</f>
         <v/>
       </c>
@@ -8430,7 +8515,7 @@
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>Normalised earnings power — every intermediate line</t>
         </is>
@@ -8580,7 +8665,7 @@
         </is>
       </c>
       <c r="B30" s="14">
-        <f>(B29-'Assumptions'!C122-'Assumptions'!C123)*(1-'Assumptions'!C107)</f>
+        <f>(B29-'Assumptions'!C127-'Assumptions'!C128)*(1-'Assumptions'!C112)</f>
         <v/>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -8712,23 +8797,23 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="25">
         <f>'Segments'!B18</f>
         <v/>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <f>'Segments'!C18</f>
         <v/>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <f>'Segments'!D18</f>
         <v/>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <f>'Segments'!E18</f>
         <v/>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <f>'Segments'!F18</f>
         <v/>
       </c>
@@ -8747,23 +8832,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="25">
         <f>'Segments'!B34</f>
         <v/>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <f>'Segments'!C34</f>
         <v/>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <f>'Segments'!D34</f>
         <v/>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <f>'Segments'!E34</f>
         <v/>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <f>'Segments'!F34</f>
         <v/>
       </c>
@@ -8809,23 +8894,23 @@
           <t>Depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="25">
         <f>'Segments'!B25</f>
         <v/>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <f>'Segments'!C25</f>
         <v/>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <f>'Segments'!D25</f>
         <v/>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <f>'Segments'!E25</f>
         <v/>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <f>'Segments'!F25</f>
         <v/>
       </c>
@@ -8864,23 +8949,23 @@
         </is>
       </c>
       <c r="B10" s="14">
-        <f>B9*(1-'Assumptions'!C107)</f>
+        <f>B9*(1-'Assumptions'!C112)</f>
         <v/>
       </c>
       <c r="C10" s="14">
-        <f>C9*(1-'Assumptions'!C107)</f>
+        <f>C9*(1-'Assumptions'!C112)</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>D9*(1-'Assumptions'!C107)</f>
+        <f>D9*(1-'Assumptions'!C112)</f>
         <v/>
       </c>
       <c r="E10" s="14">
-        <f>E9*(1-'Assumptions'!C107)</f>
+        <f>E9*(1-'Assumptions'!C112)</f>
         <v/>
       </c>
       <c r="F10" s="14">
-        <f>F9*(1-'Assumptions'!C107)</f>
+        <f>F9*(1-'Assumptions'!C112)</f>
         <v/>
       </c>
     </row>
@@ -8918,23 +9003,23 @@
         </is>
       </c>
       <c r="B12" s="14">
-        <f>-($I$5*'Assumptions'!C124+$I$6*(1-$I$5)+B5*'Assumptions'!C136)</f>
+        <f>-($I$5*'Assumptions'!C129+$I$6*(1-$I$5)+B5*'Assumptions'!C141)</f>
         <v/>
       </c>
       <c r="C12" s="14">
-        <f>-($I$5*'Assumptions'!C125+C5*'Assumptions'!C136)</f>
+        <f>-($I$5*'Assumptions'!C130+C5*'Assumptions'!C141)</f>
         <v/>
       </c>
       <c r="D12" s="14">
-        <f>-($I$5*'Assumptions'!C126+D5*'Assumptions'!C136)</f>
+        <f>-($I$5*'Assumptions'!C131+D5*'Assumptions'!C141)</f>
         <v/>
       </c>
       <c r="E12" s="14">
-        <f>-($I$5*'Assumptions'!C127+E5*'Assumptions'!C136)</f>
+        <f>-($I$5*'Assumptions'!C132+E5*'Assumptions'!C141)</f>
         <v/>
       </c>
       <c r="F12" s="14">
-        <f>-($I$5*'Assumptions'!C128+F5*'Assumptions'!C136)</f>
+        <f>-($I$5*'Assumptions'!C133+F5*'Assumptions'!C141)</f>
         <v/>
       </c>
     </row>
@@ -8944,23 +9029,23 @@
           <t>Less change in working capital</t>
         </is>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="25">
         <f>-'Cash Flow'!B12</f>
         <v/>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="25">
         <f>-'Cash Flow'!C12</f>
         <v/>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="25">
         <f>-'Cash Flow'!D12</f>
         <v/>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <f>-'Cash Flow'!E12</f>
         <v/>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <f>-'Cash Flow'!F12</f>
         <v/>
       </c>
@@ -8998,24 +9083,24 @@
           <t>Discount rate from the glide</t>
         </is>
       </c>
-      <c r="B15" s="28">
-        <f>'Assumptions'!C110</f>
-        <v/>
-      </c>
-      <c r="C15" s="28">
-        <f>'Assumptions'!C108*(('Assumptions'!C98+('Assumptions'!C113-'Assumptions'!C98)*1/5)+'Assumptions'!C97*'Assumptions'!C96)+'Assumptions'!C109*('Assumptions'!C105*'Assumptions'!C101+(1-'Assumptions'!C105)*((1+'Assumptions'!C102)*(1+'Assumptions'!C42)-1))*(1-'Assumptions'!C107)</f>
-        <v/>
-      </c>
-      <c r="D15" s="28">
-        <f>'Assumptions'!C108*(('Assumptions'!C98+('Assumptions'!C113-'Assumptions'!C98)*2/5)+'Assumptions'!C97*'Assumptions'!C96)+'Assumptions'!C109*('Assumptions'!C105*'Assumptions'!C101+(1-'Assumptions'!C105)*((1+'Assumptions'!C102)*(1+'Assumptions'!C44)-1))*(1-'Assumptions'!C107)</f>
-        <v/>
-      </c>
-      <c r="E15" s="28">
-        <f>'Assumptions'!C108*(('Assumptions'!C98+('Assumptions'!C113-'Assumptions'!C98)*3/5)+'Assumptions'!C97*'Assumptions'!C96)+'Assumptions'!C109*('Assumptions'!C105*'Assumptions'!C101+(1-'Assumptions'!C105)*((1+'Assumptions'!C102)*(1+'Assumptions'!C46)-1))*(1-'Assumptions'!C107)</f>
-        <v/>
-      </c>
-      <c r="F15" s="28">
-        <f>'Assumptions'!C108*(('Assumptions'!C98+('Assumptions'!C113-'Assumptions'!C98)*4/5)+'Assumptions'!C97*'Assumptions'!C96)+'Assumptions'!C109*('Assumptions'!C105*'Assumptions'!C101+(1-'Assumptions'!C105)*((1+'Assumptions'!C102)*(1+'Assumptions'!C48)-1))*(1-'Assumptions'!C107)</f>
+      <c r="B15" s="29">
+        <f>'Assumptions'!C115</f>
+        <v/>
+      </c>
+      <c r="C15" s="29">
+        <f>'Assumptions'!C113*(('Assumptions'!C98+('Assumptions'!C118-'Assumptions'!C98)*1/5)+'Assumptions'!C97*'Assumptions'!C103+'Assumptions'!C102)+'Assumptions'!C114*('Assumptions'!C110*'Assumptions'!C106+(1-'Assumptions'!C110)*((1+'Assumptions'!C107)*(1+'Assumptions'!C42)-1))*(1-'Assumptions'!C112)</f>
+        <v/>
+      </c>
+      <c r="D15" s="29">
+        <f>'Assumptions'!C113*(('Assumptions'!C98+('Assumptions'!C118-'Assumptions'!C98)*2/5)+'Assumptions'!C97*'Assumptions'!C103+'Assumptions'!C102)+'Assumptions'!C114*('Assumptions'!C110*'Assumptions'!C106+(1-'Assumptions'!C110)*((1+'Assumptions'!C107)*(1+'Assumptions'!C44)-1))*(1-'Assumptions'!C112)</f>
+        <v/>
+      </c>
+      <c r="E15" s="29">
+        <f>'Assumptions'!C113*(('Assumptions'!C98+('Assumptions'!C118-'Assumptions'!C98)*3/5)+'Assumptions'!C97*'Assumptions'!C103+'Assumptions'!C102)+'Assumptions'!C114*('Assumptions'!C110*'Assumptions'!C106+(1-'Assumptions'!C110)*((1+'Assumptions'!C107)*(1+'Assumptions'!C46)-1))*(1-'Assumptions'!C112)</f>
+        <v/>
+      </c>
+      <c r="F15" s="29">
+        <f>'Assumptions'!C113*(('Assumptions'!C98+('Assumptions'!C118-'Assumptions'!C98)*4/5)+'Assumptions'!C97*'Assumptions'!C103+'Assumptions'!C102)+'Assumptions'!C114*('Assumptions'!C110*'Assumptions'!C106+(1-'Assumptions'!C110)*((1+'Assumptions'!C107)*(1+'Assumptions'!C48)-1))*(1-'Assumptions'!C112)</f>
         <v/>
       </c>
     </row>
@@ -9025,23 +9110,23 @@
           <t>Discount factor, compounded</t>
         </is>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="30">
         <f>1/(1+B15)</f>
         <v/>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <f>B16/(1+C15)</f>
         <v/>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <f>C16/(1+D15)</f>
         <v/>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <f>D16/(1+E15)</f>
         <v/>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <f>E16/(1+F15)</f>
         <v/>
       </c>
@@ -9102,11 +9187,11 @@
         </is>
       </c>
       <c r="B21" s="14">
-        <f>(F9+SUM('Assumptions'!C124:C127)*'Assumptions'!C130)*(1+'Assumptions'!C117)</f>
+        <f>(F9+SUM('Assumptions'!C129:C132)*'Assumptions'!C135)*(1+'Assumptions'!C122)</f>
         <v/>
       </c>
       <c r="D21" s="14">
-        <f>(F9+SUM('Assumptions'!C124:C127)*'Assumptions'!C130)*(1+'Assumptions'!C117)</f>
+        <f>(F9+SUM('Assumptions'!C129:C132)*'Assumptions'!C135)*(1+'Assumptions'!C122)</f>
         <v/>
       </c>
     </row>
@@ -9117,11 +9202,11 @@
         </is>
       </c>
       <c r="B22" s="14">
-        <f>'Assumptions'!C139*'Assumptions'!C141*'Assumptions'!C142*('Assumptions'!C49*(1+'Assumptions'!C117-'Assumptions'!C133))/1000000</f>
+        <f>'Assumptions'!C144*'Assumptions'!C146*'Assumptions'!C147*('Assumptions'!C49*(1+'Assumptions'!C122-'Assumptions'!C138))/1000000</f>
         <v/>
       </c>
       <c r="D22" s="14">
-        <f>'Assumptions'!C139*0*'Assumptions'!C142*('Assumptions'!C49*(1+'Assumptions'!C117-'Assumptions'!C133))/1000000</f>
+        <f>'Assumptions'!C144*0*'Assumptions'!C147*('Assumptions'!C49*(1+'Assumptions'!C122-'Assumptions'!C138))/1000000</f>
         <v/>
       </c>
     </row>
@@ -9132,11 +9217,11 @@
         </is>
       </c>
       <c r="B23" s="14">
-        <f>B22*'Assumptions'!C143-'Assumptions'!C134*'Assumptions'!C135*'Assumptions'!C130</f>
+        <f>B22*'Assumptions'!C148-'Assumptions'!C139*'Assumptions'!C140*'Assumptions'!C135</f>
         <v/>
       </c>
       <c r="D23" s="14">
-        <f>D22*'Assumptions'!C143-0*'Assumptions'!C135*'Assumptions'!C130</f>
+        <f>D22*'Assumptions'!C148-0*'Assumptions'!C140*'Assumptions'!C135</f>
         <v/>
       </c>
     </row>
@@ -9162,11 +9247,11 @@
         </is>
       </c>
       <c r="B25" s="14">
-        <f>B24*(1-'Assumptions'!C107)</f>
+        <f>B24*(1-'Assumptions'!C112)</f>
         <v/>
       </c>
       <c r="D25" s="14">
-        <f>D24*(1-'Assumptions'!C107)</f>
+        <f>D24*(1-'Assumptions'!C112)</f>
         <v/>
       </c>
     </row>
@@ -9177,11 +9262,11 @@
         </is>
       </c>
       <c r="B26" s="14">
-        <f>(F8-SUM('Assumptions'!C124:C127)*'Assumptions'!C130)*(1+'Assumptions'!C117)+'Assumptions'!C134*'Assumptions'!C135*'Assumptions'!C130</f>
+        <f>(F8-SUM('Assumptions'!C129:C132)*'Assumptions'!C135)*(1+'Assumptions'!C122)+'Assumptions'!C139*'Assumptions'!C140*'Assumptions'!C135</f>
         <v/>
       </c>
       <c r="D26" s="14">
-        <f>(F8-SUM('Assumptions'!C124:C127)*'Assumptions'!C130)*(1+'Assumptions'!C117)+0*'Assumptions'!C135*'Assumptions'!C130</f>
+        <f>(F8-SUM('Assumptions'!C129:C132)*'Assumptions'!C135)*(1+'Assumptions'!C122)+0*'Assumptions'!C140*'Assumptions'!C135</f>
         <v/>
       </c>
     </row>
@@ -9192,11 +9277,11 @@
         </is>
       </c>
       <c r="B27" s="14">
-        <f>-B26*(1+'Assumptions'!C111)^'Assumptions'!C118</f>
+        <f>-B26*(1+'Assumptions'!C116)^'Assumptions'!C123</f>
         <v/>
       </c>
       <c r="D27" s="14">
-        <f>-D26*(1+'Assumptions'!C111)^'Assumptions'!C118</f>
+        <f>-D26*(1+'Assumptions'!C116)^'Assumptions'!C123</f>
         <v/>
       </c>
     </row>
@@ -9207,11 +9292,11 @@
         </is>
       </c>
       <c r="B28" s="14">
-        <f>-((1+'Assumptions'!C117)/(1+'Assumptions'!C111)-1)*(-B27*'Assumptions'!C119)</f>
+        <f>-((1+'Assumptions'!C122)/(1+'Assumptions'!C116)-1)*(-B27*'Assumptions'!C124)</f>
         <v/>
       </c>
       <c r="D28" s="14">
-        <f>-((1+'Assumptions'!C117)/(1+'Assumptions'!C111)-1)*(-D27*'Assumptions'!C119)</f>
+        <f>-((1+'Assumptions'!C122)/(1+'Assumptions'!C116)-1)*(-D27*'Assumptions'!C124)</f>
         <v/>
       </c>
     </row>
@@ -9222,11 +9307,11 @@
         </is>
       </c>
       <c r="B29" s="14">
-        <f>-'Assumptions'!C111*'Cash Flow'!F10*(1+'Assumptions'!C117)</f>
+        <f>-'Assumptions'!C116*'Cash Flow'!F10*(1+'Assumptions'!C122)</f>
         <v/>
       </c>
       <c r="D29" s="14">
-        <f>-'Assumptions'!C111*'Cash Flow'!F10*(1+'Assumptions'!C117)</f>
+        <f>-'Assumptions'!C116*'Cash Flow'!F10*(1+'Assumptions'!C122)</f>
         <v/>
       </c>
     </row>
@@ -9252,11 +9337,11 @@
         </is>
       </c>
       <c r="B31" s="14">
-        <f>B30/('Assumptions'!C116-'Assumptions'!C117)</f>
+        <f>B30/('Assumptions'!C121-'Assumptions'!C122)</f>
         <v/>
       </c>
       <c r="D31" s="14">
-        <f>D30/('Assumptions'!C116-'Assumptions'!C117)</f>
+        <f>D30/('Assumptions'!C121-'Assumptions'!C122)</f>
         <v/>
       </c>
     </row>
@@ -9267,11 +9352,11 @@
         </is>
       </c>
       <c r="B32" s="14">
-        <f>B25/'Assumptions'!C116</f>
+        <f>B25/'Assumptions'!C121</f>
         <v/>
       </c>
       <c r="D32" s="14">
-        <f>D25/'Assumptions'!C116</f>
+        <f>D25/'Assumptions'!C121</f>
         <v/>
       </c>
     </row>
@@ -9504,23 +9589,23 @@
         </is>
       </c>
       <c r="B50" s="14">
-        <f>+'Assumptions'!C124</f>
+        <f>+'Assumptions'!C129</f>
         <v/>
       </c>
       <c r="C50" s="14">
-        <f>+'Assumptions'!C125</f>
+        <f>+'Assumptions'!C130</f>
         <v/>
       </c>
       <c r="D50" s="14">
-        <f>+'Assumptions'!C126</f>
+        <f>+'Assumptions'!C131</f>
         <v/>
       </c>
       <c r="E50" s="14">
-        <f>+'Assumptions'!C127</f>
+        <f>+'Assumptions'!C132</f>
         <v/>
       </c>
       <c r="F50" s="14">
-        <f>+'Assumptions'!C128</f>
+        <f>+'Assumptions'!C133</f>
         <v/>
       </c>
     </row>
@@ -9531,7 +9616,7 @@
         </is>
       </c>
       <c r="B51" s="14">
-        <f>-'Assumptions'!C137</f>
+        <f>-'Assumptions'!C142</f>
         <v/>
       </c>
       <c r="C51" s="14">
@@ -9562,19 +9647,19 @@
         <v/>
       </c>
       <c r="C52" s="14">
-        <f>-SUM('Assumptions'!C124:C124)*'Assumptions'!C130*'Assumptions'!C107</f>
+        <f>-SUM('Assumptions'!C129:C129)*'Assumptions'!C135*'Assumptions'!C112</f>
         <v/>
       </c>
       <c r="D52" s="14">
-        <f>-SUM('Assumptions'!C124:C125)*'Assumptions'!C130*'Assumptions'!C107</f>
+        <f>-SUM('Assumptions'!C129:C130)*'Assumptions'!C135*'Assumptions'!C112</f>
         <v/>
       </c>
       <c r="E52" s="14">
-        <f>-SUM('Assumptions'!C124:C126)*'Assumptions'!C130*'Assumptions'!C107</f>
+        <f>-SUM('Assumptions'!C129:C131)*'Assumptions'!C135*'Assumptions'!C112</f>
         <v/>
       </c>
       <c r="F52" s="14">
-        <f>-SUM('Assumptions'!C124:C127)*'Assumptions'!C130*'Assumptions'!C107</f>
+        <f>-SUM('Assumptions'!C129:C132)*'Assumptions'!C135*'Assumptions'!C112</f>
         <v/>
       </c>
     </row>
@@ -9744,23 +9829,23 @@
       <c r="E5" s="13" t="n">
         <v>10378.73038</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <f>'Segments'!B18</f>
         <v/>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="25">
         <f>'Segments'!C18</f>
         <v/>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="25">
         <f>'Segments'!D18</f>
         <v/>
       </c>
-      <c r="I5" s="24">
+      <c r="I5" s="25">
         <f>'Segments'!E18</f>
         <v/>
       </c>
-      <c r="J5" s="24">
+      <c r="J5" s="25">
         <f>'Segments'!F18</f>
         <v/>
       </c>
@@ -9783,23 +9868,23 @@
       <c r="E6" s="13" t="n">
         <v>5825.213193060001</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <f>'Segments'!B26</f>
         <v/>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="25">
         <f>'Segments'!C26</f>
         <v/>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="25">
         <f>'Segments'!D26</f>
         <v/>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="25">
         <f>'Segments'!E26</f>
         <v/>
       </c>
-      <c r="J6" s="24">
+      <c r="J6" s="25">
         <f>'Segments'!F26</f>
         <v/>
       </c>
@@ -9826,23 +9911,23 @@
         <f>E5-E6</f>
         <v/>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <f>'Segments'!B27</f>
         <v/>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="25">
         <f>'Segments'!C27</f>
         <v/>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="25">
         <f>'Segments'!D27</f>
         <v/>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="25">
         <f>'Segments'!E27</f>
         <v/>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="25">
         <f>'Segments'!F27</f>
         <v/>
       </c>
@@ -9865,23 +9950,23 @@
       <c r="E8" s="13" t="n">
         <v>979.6093333333333</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <f>'Segments'!B29+'Segments'!B30</f>
         <v/>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="25">
         <f>'Segments'!C29+'Segments'!C30</f>
         <v/>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="25">
         <f>'Segments'!D29+'Segments'!D30</f>
         <v/>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="25">
         <f>'Segments'!E29+'Segments'!E30</f>
         <v/>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="25">
         <f>'Segments'!F29+'Segments'!F30</f>
         <v/>
       </c>
@@ -9904,23 +9989,23 @@
       <c r="E9" s="13" t="n">
         <v>365.108</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="25">
         <f>'Segments'!B31</f>
         <v/>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="25">
         <f>'Segments'!C31</f>
         <v/>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="25">
         <f>'Segments'!D31</f>
         <v/>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="25">
         <f>'Segments'!E31</f>
         <v/>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="25">
         <f>'Segments'!F31</f>
         <v/>
       </c>
@@ -9947,23 +10032,23 @@
         <f>E7-E8-E9</f>
         <v/>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="25">
         <f>'Segments'!B33</f>
         <v/>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="25">
         <f>'Segments'!C33</f>
         <v/>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="25">
         <f>'Segments'!D33</f>
         <v/>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="25">
         <f>'Segments'!E33</f>
         <v/>
       </c>
-      <c r="J10" s="24">
+      <c r="J10" s="25">
         <f>'Segments'!F33</f>
         <v/>
       </c>
@@ -9986,23 +10071,23 @@
       <c r="E11" s="13" t="n">
         <v>890.591</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="25">
         <f>'Segments'!B25</f>
         <v/>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="25">
         <f>'Segments'!C25</f>
         <v/>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="25">
         <f>'Segments'!D25</f>
         <v/>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="25">
         <f>'Segments'!E25</f>
         <v/>
       </c>
-      <c r="J11" s="24">
+      <c r="J11" s="25">
         <f>'Segments'!F25</f>
         <v/>
       </c>
@@ -10029,23 +10114,23 @@
         <f>E10+E11</f>
         <v/>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="25">
         <f>'Segments'!B34</f>
         <v/>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="25">
         <f>'Segments'!C34</f>
         <v/>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="25">
         <f>'Segments'!D34</f>
         <v/>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="25">
         <f>'Segments'!E34</f>
         <v/>
       </c>
-      <c r="J12" s="24">
+      <c r="J12" s="25">
         <f>'Segments'!F34</f>
         <v/>
       </c>

--- a/engine/egch_study/EGCH_Valuation_Model_10092026.xlsx
+++ b/engine/egch_study/EGCH_Valuation_Model_10092026.xlsx
@@ -1478,11 +1478,11 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Opening net working capital, 31 March 2026 as reported</t>
+          <t>Opening net working capital, 31 March 2026 as reported, net of the documentary credits inside the inventory line (note 11)</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>3069.424</v>
+        <v>1662.024</v>
       </c>
     </row>
     <row r="12">
@@ -2884,11 +2884,11 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>No duty at all (8.0006) or half the rate (6.5115)</t>
+          <t>No duty at all (8.0748) or half the rate (6.5857)</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>8.000565434916803</v>
+        <v>8.074785424029702</v>
       </c>
       <c r="D17" s="11">
         <f>C17-$D$15</f>
@@ -2898,16 +2898,16 @@
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>The new complex's granulated ammonium nitrate priced at a typed US$280/t, the weakest-sourced input in a 304-input register</t>
+          <t>The new complex's granulated ammonium nitrate priced at the SAME PRODUCT'S OWN DISCLOSED REALISED PRICE — EGP 20,000/t from note 20, carried on the currency exactly as the existing nitrate business is</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Priced at the SAME PRODUCT'S OWN DISCLOSED REALISED PRICE — EGP 20,000/t from note 20, which is US$408.16/t at this model's FY2024/25 rate of 49.00 (5.5970)</t>
+          <t>Priced at the retired typed US$280/t, the weakest-sourced input in a 304-input register, whose source string was four words long and named no assessor, series, date or basis (4.5220)</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>5.597036900779846</v>
+        <v>4.522010640726562</v>
       </c>
       <c r="D18" s="11">
         <f>C18-$D$15</f>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>3.102900059761477</v>
+        <v>3.013766059535749</v>
       </c>
       <c r="D19" s="11">
         <f>C19-$D$15</f>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>1.47809148744809</v>
+        <v>1.239670920388017</v>
       </c>
       <c r="D20" s="11">
         <f>C20-$D$15</f>
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>2.980526510171584</v>
+        <v>2.873455957180482</v>
       </c>
       <c r="D21" s="11">
         <f>C21-$D$15</f>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>3.548742891573957</v>
+        <v>3.492009478081763</v>
       </c>
       <c r="D22" s="11">
         <f>C22-$D$15</f>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>5.899684651558272</v>
+        <v>6.046391624064186</v>
       </c>
       <c r="D23" s="11">
         <f>C23-$D$15</f>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>2.020338775157204</v>
+        <v>2.094558764270101</v>
       </c>
       <c r="D24" s="11">
         <f>C24-$D$15</f>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>5.524568506724146</v>
+        <v>5.828637745670282</v>
       </c>
       <c r="D25" s="11">
         <f>C25-$D$15</f>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>4.104580574764806</v>
+        <v>4.178800563877706</v>
       </c>
       <c r="D26" s="11">
         <f>C26-$D$15</f>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>2.404702110064437</v>
+        <v>2.478922099177338</v>
       </c>
       <c r="D27" s="11">
         <f>C27-$D$15</f>
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>5.957407998331238</v>
+        <v>6.031627987444139</v>
       </c>
       <c r="D28" s="11">
         <f>C28-$D$15</f>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>4.817637069790051</v>
+        <v>4.891857058902947</v>
       </c>
       <c r="D29" s="11">
         <f>C29-$D$15</f>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="B25" s="15" t="n">
-        <v>0.1300292595239384</v>
+        <v>0.1324201241345537</v>
       </c>
     </row>
     <row r="26">
@@ -3929,7 +3929,7 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>9.128793547103569</v>
+        <v>8.628390411633379</v>
       </c>
     </row>
     <row r="37">
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>6.315558537881176</v>
+        <v>6.374373403232003</v>
       </c>
     </row>
     <row r="39">
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>5.022413776196755</v>
+        <v>5.096633765309656</v>
       </c>
     </row>
     <row r="24">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>9.128793547103569</v>
+        <v>8.628390411633379</v>
       </c>
     </row>
     <row r="25">
@@ -4301,7 +4301,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>15.98773106857623</v>
+        <v>16.05127074420128</v>
       </c>
     </row>
     <row r="27">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>4.289630624386951</v>
+        <v>4.353170300012002</v>
       </c>
     </row>
     <row r="28"/>
@@ -7047,22 +7047,22 @@
       </c>
     </row>
     <row r="147" ht="14" customHeight="1">
-      <c r="A147" s="7" t="inlineStr">
-        <is>
-          <t>Nitrate price</t>
+      <c r="A147" s="10" t="inlineStr">
+        <is>
+          <t>Nitrate price — the company's own disclosed realisation, carried on the currency</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>US$/tonne</t>
+          <t>US$/tonne equivalent</t>
         </is>
       </c>
       <c r="C147" s="13" t="n">
-        <v>280</v>
+        <v>408.1632653061225</v>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>Mid-cycle ammonium nitrate pricing</t>
+          <t>reviewed interims, note 20 — EGP 20,000/t realised</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9464,7 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>1382.886</v>
+        <v>1509.1125852</v>
       </c>
       <c r="D42" s="14">
         <f>B42</f>

--- a/engine/egch_study/EGCH_Valuation_Model_10092026.xlsx
+++ b/engine/egch_study/EGCH_Valuation_Model_10092026.xlsx
@@ -2879,16 +2879,16 @@
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>A 10% ad-valorem export duty charged on every export tonne, for ever</t>
+          <t>No export duty, because Ministerial Decision 340 of 2026 cancelled the levy with effect from 1 August 2026 — five weeks before this study's strike</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>No duty at all (8.0748) or half the rate (6.5857)</t>
+          <t>The 10% ad-valorem duty back, charged on every export tonne for ever (5.0966), or at half that rate (6.5857)</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>8.074785424029702</v>
+        <v>5.096633765309656</v>
       </c>
       <c r="D17" s="11">
         <f>C17-$D$15</f>
@@ -2903,11 +2903,11 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Priced at the retired typed US$280/t, the weakest-sourced input in a 304-input register, whose source string was four words long and named no assessor, series, date or basis (4.5220)</t>
+          <t>Priced at the retired typed US$280/t, the weakest-sourced input in a 304-input register, whose source string was four words long and named no assessor, series, date or basis (7.5002)</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>4.522010640726562</v>
+        <v>7.500162299446612</v>
       </c>
       <c r="D18" s="11">
         <f>C18-$D$15</f>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>3.013766059535749</v>
+        <v>5.407252661808486</v>
       </c>
       <c r="D19" s="11">
         <f>C19-$D$15</f>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>1.239670920388017</v>
+        <v>3.145577030925056</v>
       </c>
       <c r="D20" s="11">
         <f>C20-$D$15</f>
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>2.873455957180482</v>
+        <v>5.264107281415742</v>
       </c>
       <c r="D21" s="11">
         <f>C21-$D$15</f>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>3.492009478081763</v>
+        <v>6.027419537013731</v>
       </c>
       <c r="D22" s="11">
         <f>C22-$D$15</f>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>6.046391624064186</v>
+        <v>9.293905460682925</v>
       </c>
       <c r="D23" s="11">
         <f>C23-$D$15</f>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>2.094558764270101</v>
+        <v>5.072710422990149</v>
       </c>
       <c r="D24" s="11">
         <f>C24-$D$15</f>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>5.828637745670282</v>
+        <v>8.806789404390324</v>
       </c>
       <c r="D25" s="11">
         <f>C25-$D$15</f>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>4.178800563877706</v>
+        <v>7.082167477332161</v>
       </c>
       <c r="D26" s="11">
         <f>C26-$D$15</f>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>2.478922099177338</v>
+        <v>5.457073757897384</v>
       </c>
       <c r="D27" s="11">
         <f>C27-$D$15</f>
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>6.031627987444139</v>
+        <v>9.009779646164183</v>
       </c>
       <c r="D28" s="11">
         <f>C28-$D$15</f>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>4.891857058902947</v>
+        <v>7.870008717622996</v>
       </c>
       <c r="D29" s="11">
         <f>C29-$D$15</f>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="B25" s="15" t="n">
-        <v>0.1324201241345537</v>
+        <v>0.1498136460228862</v>
       </c>
     </row>
     <row r="26">
@@ -3929,7 +3929,7 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>8.628390411633379</v>
+        <v>11.60654207035342</v>
       </c>
     </row>
     <row r="37">
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>6.374373403232003</v>
+        <v>9.092881689457943</v>
       </c>
     </row>
     <row r="39">
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>5.096633765309656</v>
+        <v>8.074785424029702</v>
       </c>
     </row>
     <row r="24">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>8.628390411633379</v>
+        <v>11.60654207035342</v>
       </c>
     </row>
     <row r="25">
@@ -4301,7 +4301,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>16.05127074420128</v>
+        <v>19.92933486792083</v>
       </c>
     </row>
     <row r="27">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>4.353170300012002</v>
+        <v>7.366806375302057</v>
       </c>
     </row>
     <row r="28"/>
@@ -5260,11 +5260,11 @@
         </is>
       </c>
       <c r="C50" s="15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>Decree No. 258 of 2026 of the Minister of Investment and Foreign Trade, published in the Official Gazette on 25 June 2026 — 10% ad valorem on the FOB invoice value of nitrogen fertiliser exports, the invoice certified by the Chamber of Chemical Industries. It replaced a temporary US$90/t duty imposed in May 2026 for three months; the 10% carries no stated expiry. Pure ammonium nitrate above 34.2% nitrogen and free zone shipments are exempt — urea is neither. Read from two independent reports of the instrument rather than the Gazette text, which is the remaining gap in this citation</t>
+          <t>Ministerial Decision 340 of 2026, effective 1 August 2026, cancelling Decisions 190, 203 and 258 of 2026 and ending the 10% ad valorem export levy on nitrogen fertilisers. The Egyptian Customs Authority issued Circular 46 of 2026 to govern shipments whose declarations were opened before the levy ceased, which is the administrative trace a cancellation leaves and a rumour does not. This study strikes on 3 September 2026, so the rate in force at the strike is nil. The superseded chain is registered below with its own dates, because a duty that existed for three months is a fact about this year and the alternatives grid prices its return</t>
         </is>
       </c>
     </row>

--- a/engine/egch_study/EGCH_Valuation_Model_10092026.xlsx
+++ b/engine/egch_study/EGCH_Valuation_Model_10092026.xlsx
@@ -2725,19 +2725,19 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>-2.62</v>
+        <v>-0.34</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>-2.74</v>
+        <v>-0.71</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>-2.86</v>
+        <v>-1.06</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>-2.93</v>
+        <v>-1.28</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>-3.01</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="7">
@@ -2747,19 +2747,19 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>-0.35</v>
+        <v>2.15</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>-0.66</v>
+        <v>1.58</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>-0.95</v>
+        <v>1.04</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>-1.13</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>-1.32</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="8">
@@ -2769,19 +2769,19 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>1.92</v>
+        <v>4.65</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>1.43</v>
+        <v>3.87</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>0.96</v>
+        <v>3.14</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>0.66</v>
+        <v>2.67</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>0.37</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
@@ -2791,19 +2791,19 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>4.19</v>
+        <v>7.14</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>3.52</v>
+        <v>6.17</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>2.88</v>
+        <v>5.24</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>2.46</v>
+        <v>4.64</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>2.06</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="10">
@@ -2813,19 +2813,19 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>6.47</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>5.6</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>4.79</v>
+        <v>7.34</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>4.26</v>
+        <v>6.62</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>3.74</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="11"/>
